--- a/EXCEL/Exercise Files/Chapter02/02_04_Trendline.xlsx
+++ b/EXCEL/Exercise Files/Chapter02/02_04_Trendline.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curt\Desktop\Exercise Files\Chapter02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter02\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A64698-7133-4233-9B4C-2E897AA42DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14820"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -110,7 +111,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -182,6 +182,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$A$2:$A$27</c:f>
@@ -357,8 +371,14 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0F0D-4F45-A4B5-13A23382FA49}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -501,6 +521,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1111,7 +1162,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1391,15 +1448,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1407,7 +1464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1415,7 +1472,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1423,7 +1480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1431,7 +1488,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1439,7 +1496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1447,7 +1504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1455,7 +1512,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10</v>
       </c>
@@ -1463,7 +1520,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>20</v>
       </c>
@@ -1471,7 +1528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>20</v>
       </c>
@@ -1479,7 +1536,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>22</v>
       </c>
@@ -1487,7 +1544,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>45</v>
       </c>
@@ -1495,7 +1552,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>50</v>
       </c>
@@ -1503,7 +1560,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>50</v>
       </c>
@@ -1511,7 +1568,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>50</v>
       </c>
@@ -1519,7 +1576,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>75</v>
       </c>
@@ -1527,7 +1584,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>75</v>
       </c>
@@ -1535,7 +1592,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>75</v>
       </c>
@@ -1543,7 +1600,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>75</v>
       </c>
@@ -1551,7 +1608,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>85</v>
       </c>
@@ -1559,7 +1616,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>87</v>
       </c>
@@ -1567,7 +1624,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>99</v>
       </c>
@@ -1575,7 +1632,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>100</v>
       </c>
@@ -1583,7 +1640,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>125</v>
       </c>
@@ -1591,7 +1648,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>130</v>
       </c>
@@ -1599,7 +1656,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>145</v>
       </c>
@@ -1607,7 +1664,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>152</v>
       </c>
